--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.03498025257488</v>
+        <v>5.205684291043418</v>
       </c>
       <c r="D2" t="n">
-        <v>30.5186898978301</v>
+        <v>4.959287108397392</v>
       </c>
       <c r="E2" t="n">
-        <v>4.811880174362861</v>
+        <v>0.7819305283339648</v>
       </c>
       <c r="F2" t="n">
-        <v>4.822471545631807</v>
+        <v>0.7836516261651687</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.41121990384916</v>
+        <v>3.641823234375489</v>
       </c>
       <c r="D3" t="n">
-        <v>20.87374680656649</v>
+        <v>3.391983856067055</v>
       </c>
       <c r="E3" t="n">
-        <v>4.811880174362861</v>
+        <v>0.7819305283339648</v>
       </c>
       <c r="F3" t="n">
-        <v>4.822471545631807</v>
+        <v>0.7836516261651687</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
